--- a/test/excel/win/parts/frozen-held/delete-col-b.xlsx
+++ b/test/excel/win/parts/frozen-held/delete-col-b.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xlcalc\work\parts-frozen-held-50306-1\out\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xlcalc\work\parts-frozen-held-27825-1\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C943F16-B46F-409A-B4EB-6137F87582AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{731EA0A3-84E0-44ED-A0CE-C6BE68DDCE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
